--- a/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
+++ b/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
@@ -13255,36 +13255,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13337,6 +13307,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -14110,11 +14110,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="138521600"/>
-        <c:axId val="138535680"/>
+        <c:axId val="105451520"/>
+        <c:axId val="105453056"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="138521600"/>
+        <c:axId val="105451520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14152,14 +14152,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="138535680"/>
+        <c:crossAx val="105453056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="138535680"/>
+        <c:axId val="105453056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14203,7 +14203,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="138521600"/>
+        <c:crossAx val="105451520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14296,7 +14296,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14339,7 +14339,7 @@
         <xdr:cNvPr id="210843" name="Group 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14360,7 +14360,7 @@
           <xdr:cNvPr id="3" name="Rectangle 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14435,7 +14435,7 @@
           <xdr:cNvPr id="4" name="Rectangle 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14505,7 +14505,7 @@
           <xdr:cNvPr id="5" name="Rectangle 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14591,7 +14591,7 @@
         <xdr:cNvPr id="6" name="Rectangle 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15117,12 +15117,14 @@
     <col min="2" max="2" width="16.42578125" style="244" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="264" customWidth="1"/>
     <col min="4" max="4" width="22.28515625" style="264" customWidth="1"/>
-    <col min="5" max="5" width="9" style="258" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="244" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" style="258" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="244" customWidth="1"/>
     <col min="7" max="7" width="30.42578125" style="244" customWidth="1"/>
     <col min="8" max="9" width="12.5703125" style="244" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" style="268" customWidth="1"/>
-    <col min="11" max="13" width="10.42578125" style="244" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="244" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="244" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="244" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="244" customWidth="1"/>
     <col min="15" max="15" width="12" style="265" customWidth="1"/>
     <col min="16" max="16" width="15.7109375" style="265" customWidth="1"/>
@@ -15238,81 +15240,81 @@
       <c r="Q5" s="261"/>
     </row>
     <row r="6" spans="1:19" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A6" s="273" t="s">
+      <c r="A6" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="281" t="s">
+      <c r="B6" s="299" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="277" t="s">
+      <c r="C6" s="295" t="s">
         <v>3627</v>
       </c>
-      <c r="D6" s="277" t="s">
+      <c r="D6" s="295" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="285" t="s">
+      <c r="E6" s="275" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="293" t="s">
+      <c r="F6" s="283" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="279" t="s">
+      <c r="G6" s="297" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="287" t="s">
+      <c r="H6" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="288"/>
-      <c r="J6" s="275" t="s">
+      <c r="I6" s="278"/>
+      <c r="J6" s="293" t="s">
         <v>3870</v>
       </c>
-      <c r="K6" s="297" t="s">
+      <c r="K6" s="287" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="298"/>
-      <c r="M6" s="299" t="s">
+      <c r="L6" s="288"/>
+      <c r="M6" s="289" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="295" t="s">
+      <c r="N6" s="285" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="292" t="s">
+      <c r="O6" s="282" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="283" t="s">
+      <c r="P6" s="273" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="289" t="s">
+      <c r="Q6" s="279" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="290"/>
-      <c r="S6" s="291"/>
+      <c r="R6" s="280"/>
+      <c r="S6" s="281"/>
     </row>
     <row r="7" spans="1:19" ht="27.75" customHeight="1">
-      <c r="A7" s="274"/>
-      <c r="B7" s="282"/>
-      <c r="C7" s="278"/>
-      <c r="D7" s="278"/>
-      <c r="E7" s="286"/>
-      <c r="F7" s="294"/>
-      <c r="G7" s="280"/>
+      <c r="A7" s="292"/>
+      <c r="B7" s="300"/>
+      <c r="C7" s="296"/>
+      <c r="D7" s="296"/>
+      <c r="E7" s="276"/>
+      <c r="F7" s="284"/>
+      <c r="G7" s="298"/>
       <c r="H7" s="267" t="s">
         <v>3871</v>
       </c>
       <c r="I7" s="262" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="276"/>
+      <c r="J7" s="294"/>
       <c r="K7" s="263" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="263" t="s">
         <v>3872</v>
       </c>
-      <c r="M7" s="300"/>
-      <c r="N7" s="296"/>
-      <c r="O7" s="284"/>
-      <c r="P7" s="284"/>
+      <c r="M7" s="290"/>
+      <c r="N7" s="286"/>
+      <c r="O7" s="274"/>
+      <c r="P7" s="274"/>
       <c r="Q7" s="271" t="s">
         <v>3867</v>
       </c>
@@ -15325,6 +15327,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="H6:I6"/>
@@ -15334,12 +15342,6 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.23622047244094499" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>

--- a/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
+++ b/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
@@ -12443,7 +12443,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -13255,60 +13255,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -13339,6 +13285,57 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13350,6 +13347,30 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="23" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="25" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="30" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="31" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="34" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="34" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -14056,7 +14077,7 @@
             <c:numRef>
               <c:f>'DETAIL '!$O$7:$O$7</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -14110,11 +14131,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="105451520"/>
-        <c:axId val="105453056"/>
+        <c:axId val="148548608"/>
+        <c:axId val="148562688"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="105451520"/>
+        <c:axId val="148548608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14152,14 +14173,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105453056"/>
+        <c:crossAx val="148562688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="105453056"/>
+        <c:axId val="148562688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14203,7 +14224,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105451520"/>
+        <c:crossAx val="148548608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14296,7 +14317,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14339,7 +14360,7 @@
         <xdr:cNvPr id="210843" name="Group 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14360,7 +14381,7 @@
           <xdr:cNvPr id="3" name="Rectangle 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14435,7 +14456,7 @@
           <xdr:cNvPr id="4" name="Rectangle 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14505,7 +14526,7 @@
           <xdr:cNvPr id="5" name="Rectangle 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14591,7 +14612,7 @@
         <xdr:cNvPr id="6" name="Rectangle 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15126,7 +15147,7 @@
     <col min="12" max="12" width="14.42578125" style="244" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" style="244" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="244" customWidth="1"/>
-    <col min="15" max="15" width="12" style="265" customWidth="1"/>
+    <col min="15" max="15" width="12" style="311" customWidth="1"/>
     <col min="16" max="16" width="15.7109375" style="265" customWidth="1"/>
     <col min="17" max="17" width="18.85546875" style="265" customWidth="1"/>
     <col min="18" max="18" width="11.85546875" style="244" customWidth="1"/>
@@ -15151,7 +15172,7 @@
       <c r="L1" s="269"/>
       <c r="M1" s="269"/>
       <c r="N1" s="269"/>
-      <c r="O1" s="269"/>
+      <c r="O1" s="304"/>
       <c r="P1" s="243"/>
       <c r="Q1" s="243"/>
     </row>
@@ -15170,7 +15191,7 @@
       <c r="L2" s="270"/>
       <c r="M2" s="270"/>
       <c r="N2" s="270"/>
-      <c r="O2" s="270"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="243"/>
       <c r="Q2" s="243"/>
     </row>
@@ -15189,7 +15210,7 @@
       <c r="L3" s="246"/>
       <c r="M3" s="246"/>
       <c r="N3" s="246"/>
-      <c r="O3" s="248"/>
+      <c r="O3" s="306"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
     </row>
@@ -15217,7 +15238,7 @@
       <c r="L4" s="253"/>
       <c r="M4" s="253"/>
       <c r="N4" s="253"/>
-      <c r="O4" s="255"/>
+      <c r="O4" s="307"/>
       <c r="P4" s="255"/>
       <c r="Q4" s="255"/>
     </row>
@@ -15235,86 +15256,86 @@
       <c r="L5" s="260"/>
       <c r="M5" s="260"/>
       <c r="N5" s="260"/>
-      <c r="O5" s="261"/>
+      <c r="O5" s="308"/>
       <c r="P5" s="261"/>
       <c r="Q5" s="261"/>
     </row>
     <row r="6" spans="1:19" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A6" s="291" t="s">
+      <c r="A6" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="299" t="s">
+      <c r="B6" s="281" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="295" t="s">
+      <c r="C6" s="277" t="s">
         <v>3627</v>
       </c>
-      <c r="D6" s="295" t="s">
+      <c r="D6" s="277" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="275" t="s">
+      <c r="E6" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="283" t="s">
+      <c r="F6" s="292" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="297" t="s">
+      <c r="G6" s="279" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="277" t="s">
+      <c r="H6" s="287" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="278"/>
-      <c r="J6" s="293" t="s">
+      <c r="I6" s="288"/>
+      <c r="J6" s="275" t="s">
         <v>3870</v>
       </c>
-      <c r="K6" s="287" t="s">
+      <c r="K6" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="288"/>
-      <c r="M6" s="289" t="s">
+      <c r="L6" s="297"/>
+      <c r="M6" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="285" t="s">
+      <c r="N6" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="282" t="s">
+      <c r="O6" s="309" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="273" t="s">
+      <c r="P6" s="283" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="279" t="s">
+      <c r="Q6" s="289" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="280"/>
-      <c r="S6" s="281"/>
+      <c r="R6" s="290"/>
+      <c r="S6" s="291"/>
     </row>
     <row r="7" spans="1:19" ht="27.75" customHeight="1">
-      <c r="A7" s="292"/>
-      <c r="B7" s="300"/>
-      <c r="C7" s="296"/>
-      <c r="D7" s="296"/>
-      <c r="E7" s="276"/>
-      <c r="F7" s="284"/>
-      <c r="G7" s="298"/>
+      <c r="A7" s="274"/>
+      <c r="B7" s="282"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="278"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="293"/>
+      <c r="G7" s="280"/>
       <c r="H7" s="267" t="s">
         <v>3871</v>
       </c>
       <c r="I7" s="262" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="294"/>
+      <c r="J7" s="276"/>
       <c r="K7" s="263" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="263" t="s">
         <v>3872</v>
       </c>
-      <c r="M7" s="290"/>
-      <c r="N7" s="286"/>
-      <c r="O7" s="274"/>
-      <c r="P7" s="274"/>
+      <c r="M7" s="299"/>
+      <c r="N7" s="295"/>
+      <c r="O7" s="310"/>
+      <c r="P7" s="284"/>
       <c r="Q7" s="271" t="s">
         <v>3867</v>
       </c>
@@ -15327,12 +15348,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="H6:I6"/>
@@ -15342,6 +15357,12 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:M7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.23622047244094499" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
@@ -15382,39 +15403,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="300" t="s">
         <v>1237</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="302"/>
-      <c r="J1" s="302"/>
-      <c r="K1" s="302"/>
-      <c r="L1" s="302"/>
-      <c r="M1" s="302"/>
-      <c r="N1" s="301"/>
-      <c r="O1" s="301"/>
-      <c r="P1" s="301"/>
-      <c r="Q1" s="301"/>
+      <c r="B1" s="300"/>
+      <c r="C1" s="300"/>
+      <c r="D1" s="300"/>
+      <c r="E1" s="300"/>
+      <c r="F1" s="300"/>
+      <c r="G1" s="300"/>
+      <c r="H1" s="300"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
+      <c r="N1" s="300"/>
+      <c r="O1" s="300"/>
+      <c r="P1" s="300"/>
+      <c r="Q1" s="300"/>
       <c r="S1" s="1" t="s">
         <v>1238</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="6" customFormat="1" ht="31.15" customHeight="1">
-      <c r="A2" s="303" t="s">
+      <c r="A2" s="302" t="s">
         <v>1239</v>
       </c>
-      <c r="B2" s="303"/>
-      <c r="C2" s="303"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="303"/>
-      <c r="F2" s="303"/>
-      <c r="G2" s="303"/>
+      <c r="B2" s="302"/>
+      <c r="C2" s="302"/>
+      <c r="D2" s="303"/>
+      <c r="E2" s="302"/>
+      <c r="F2" s="302"/>
+      <c r="G2" s="302"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>

--- a/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
+++ b/api/src/TAKAHATA.Api/Templates/detail_template.xlsx
@@ -12443,7 +12443,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -13255,42 +13255,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13336,6 +13300,36 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13348,28 +13342,49 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="23" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="25" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="30" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="31" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="34" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="34" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14077,7 +14092,7 @@
             <c:numRef>
               <c:f>'DETAIL '!$O$7:$O$7</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -14118,7 +14133,7 @@
             <c:numRef>
               <c:f>'DETAIL '!$P$7:$P$7</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -14131,11 +14146,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="148548608"/>
-        <c:axId val="148562688"/>
+        <c:axId val="142978048"/>
+        <c:axId val="142992128"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="148548608"/>
+        <c:axId val="142978048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14173,14 +14188,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="148562688"/>
+        <c:crossAx val="142992128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="148562688"/>
+        <c:axId val="142992128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14224,7 +14239,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="148548608"/>
+        <c:crossAx val="142978048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14317,7 +14332,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{042FA6C6-A9A6-B020-0B1E-06FF741790E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14360,7 +14375,7 @@
         <xdr:cNvPr id="210843" name="Group 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E441A73F-6BDA-F1EC-8A02-B0FEF638374D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14381,7 +14396,7 @@
           <xdr:cNvPr id="3" name="Rectangle 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB311355-5A13-3CE4-04AD-EBD423245796}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14456,7 +14471,7 @@
           <xdr:cNvPr id="4" name="Rectangle 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DDA0C9F-6125-69F0-C735-56A1D79E75C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14526,7 +14541,7 @@
           <xdr:cNvPr id="5" name="Rectangle 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{66DCDBC1-B5EE-4256-EE82-D65A8ADBF313}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14612,7 +14627,7 @@
         <xdr:cNvPr id="6" name="Rectangle 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4891A1A4-CFC8-B7BC-616E-060F77A4F404}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15147,8 +15162,8 @@
     <col min="12" max="12" width="14.42578125" style="244" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" style="244" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="244" customWidth="1"/>
-    <col min="15" max="15" width="12" style="311" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="265" customWidth="1"/>
+    <col min="15" max="15" width="12" style="309" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" style="316" customWidth="1"/>
     <col min="17" max="17" width="18.85546875" style="265" customWidth="1"/>
     <col min="18" max="18" width="11.85546875" style="244" customWidth="1"/>
     <col min="19" max="19" width="20.28515625" style="244" customWidth="1"/>
@@ -15172,8 +15187,8 @@
       <c r="L1" s="269"/>
       <c r="M1" s="269"/>
       <c r="N1" s="269"/>
-      <c r="O1" s="304"/>
-      <c r="P1" s="243"/>
+      <c r="O1" s="302"/>
+      <c r="P1" s="310"/>
       <c r="Q1" s="243"/>
     </row>
     <row r="2" spans="1:19" ht="4.5" customHeight="1" thickBot="1">
@@ -15191,8 +15206,8 @@
       <c r="L2" s="270"/>
       <c r="M2" s="270"/>
       <c r="N2" s="270"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="243"/>
+      <c r="O2" s="303"/>
+      <c r="P2" s="310"/>
       <c r="Q2" s="243"/>
     </row>
     <row r="3" spans="1:19" ht="6.75" customHeight="1" thickTop="1">
@@ -15210,8 +15225,8 @@
       <c r="L3" s="246"/>
       <c r="M3" s="246"/>
       <c r="N3" s="246"/>
-      <c r="O3" s="306"/>
-      <c r="P3" s="248"/>
+      <c r="O3" s="304"/>
+      <c r="P3" s="311"/>
       <c r="Q3" s="248"/>
     </row>
     <row r="4" spans="1:19" s="254" customFormat="1" ht="31.5" customHeight="1">
@@ -15238,8 +15253,8 @@
       <c r="L4" s="253"/>
       <c r="M4" s="253"/>
       <c r="N4" s="253"/>
-      <c r="O4" s="307"/>
-      <c r="P4" s="255"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="312"/>
       <c r="Q4" s="255"/>
     </row>
     <row r="5" spans="1:19" s="257" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
@@ -15256,86 +15271,86 @@
       <c r="L5" s="260"/>
       <c r="M5" s="260"/>
       <c r="N5" s="260"/>
-      <c r="O5" s="308"/>
-      <c r="P5" s="261"/>
+      <c r="O5" s="306"/>
+      <c r="P5" s="313"/>
       <c r="Q5" s="261"/>
     </row>
     <row r="6" spans="1:19" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A6" s="273" t="s">
+      <c r="A6" s="288" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="281" t="s">
+      <c r="B6" s="296" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="277" t="s">
+      <c r="C6" s="292" t="s">
         <v>3627</v>
       </c>
-      <c r="D6" s="277" t="s">
+      <c r="D6" s="292" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="285" t="s">
+      <c r="E6" s="273" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="292" t="s">
+      <c r="F6" s="280" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="279" t="s">
+      <c r="G6" s="294" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="287" t="s">
+      <c r="H6" s="275" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="288"/>
-      <c r="J6" s="275" t="s">
+      <c r="I6" s="276"/>
+      <c r="J6" s="290" t="s">
         <v>3870</v>
       </c>
-      <c r="K6" s="296" t="s">
+      <c r="K6" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="297"/>
-      <c r="M6" s="298" t="s">
+      <c r="L6" s="285"/>
+      <c r="M6" s="286" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="294" t="s">
+      <c r="N6" s="282" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="309" t="s">
+      <c r="O6" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="283" t="s">
+      <c r="P6" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="289" t="s">
+      <c r="Q6" s="277" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="290"/>
-      <c r="S6" s="291"/>
+      <c r="R6" s="278"/>
+      <c r="S6" s="279"/>
     </row>
     <row r="7" spans="1:19" ht="27.75" customHeight="1">
-      <c r="A7" s="274"/>
-      <c r="B7" s="282"/>
-      <c r="C7" s="278"/>
-      <c r="D7" s="278"/>
-      <c r="E7" s="286"/>
-      <c r="F7" s="293"/>
-      <c r="G7" s="280"/>
+      <c r="A7" s="289"/>
+      <c r="B7" s="297"/>
+      <c r="C7" s="293"/>
+      <c r="D7" s="293"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="295"/>
       <c r="H7" s="267" t="s">
         <v>3871</v>
       </c>
       <c r="I7" s="262" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="276"/>
+      <c r="J7" s="291"/>
       <c r="K7" s="263" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="263" t="s">
         <v>3872</v>
       </c>
-      <c r="M7" s="299"/>
-      <c r="N7" s="295"/>
-      <c r="O7" s="310"/>
-      <c r="P7" s="284"/>
+      <c r="M7" s="287"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="308"/>
+      <c r="P7" s="315"/>
       <c r="Q7" s="271" t="s">
         <v>3867</v>
       </c>
@@ -15348,6 +15363,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="H6:I6"/>
@@ -15357,12 +15378,6 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.23622047244094499" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
@@ -15403,39 +15418,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A1" s="300" t="s">
+      <c r="A1" s="298" t="s">
         <v>1237</v>
       </c>
-      <c r="B1" s="300"/>
-      <c r="C1" s="300"/>
-      <c r="D1" s="300"/>
-      <c r="E1" s="300"/>
-      <c r="F1" s="300"/>
-      <c r="G1" s="300"/>
-      <c r="H1" s="300"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
-      <c r="N1" s="300"/>
-      <c r="O1" s="300"/>
-      <c r="P1" s="300"/>
-      <c r="Q1" s="300"/>
+      <c r="B1" s="298"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="298"/>
+      <c r="E1" s="298"/>
+      <c r="F1" s="298"/>
+      <c r="G1" s="298"/>
+      <c r="H1" s="298"/>
+      <c r="I1" s="299"/>
+      <c r="J1" s="299"/>
+      <c r="K1" s="299"/>
+      <c r="L1" s="299"/>
+      <c r="M1" s="299"/>
+      <c r="N1" s="298"/>
+      <c r="O1" s="298"/>
+      <c r="P1" s="298"/>
+      <c r="Q1" s="298"/>
       <c r="S1" s="1" t="s">
         <v>1238</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="6" customFormat="1" ht="31.15" customHeight="1">
-      <c r="A2" s="302" t="s">
+      <c r="A2" s="300" t="s">
         <v>1239</v>
       </c>
-      <c r="B2" s="302"/>
-      <c r="C2" s="302"/>
-      <c r="D2" s="303"/>
-      <c r="E2" s="302"/>
-      <c r="F2" s="302"/>
-      <c r="G2" s="302"/>
+      <c r="B2" s="300"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="301"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
+      <c r="G2" s="300"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
